--- a/artfynd/A 9197-2026 artfynd.xlsx
+++ b/artfynd/A 9197-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1516,6 +1516,218 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131538171</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57067</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Dammen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>567286</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6995088</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131538191</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57067</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Dammen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>567309</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6995090</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9197-2026 artfynd.xlsx
+++ b/artfynd/A 9197-2026 artfynd.xlsx
@@ -1521,7 +1521,7 @@
         <v>131538171</v>
       </c>
       <c r="B10" t="n">
-        <v>57067</v>
+        <v>57070</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>131538191</v>
       </c>
       <c r="B11" t="n">
-        <v>57067</v>
+        <v>57070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 9197-2026 artfynd.xlsx
+++ b/artfynd/A 9197-2026 artfynd.xlsx
@@ -1521,7 +1521,7 @@
         <v>131538171</v>
       </c>
       <c r="B10" t="n">
-        <v>57070</v>
+        <v>57071</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>131538191</v>
       </c>
       <c r="B11" t="n">
-        <v>57070</v>
+        <v>57071</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 9197-2026 artfynd.xlsx
+++ b/artfynd/A 9197-2026 artfynd.xlsx
@@ -1521,7 +1521,7 @@
         <v>131538171</v>
       </c>
       <c r="B10" t="n">
-        <v>57071</v>
+        <v>57077</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>131538191</v>
       </c>
       <c r="B11" t="n">
-        <v>57071</v>
+        <v>57077</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 9197-2026 artfynd.xlsx
+++ b/artfynd/A 9197-2026 artfynd.xlsx
@@ -1521,7 +1521,7 @@
         <v>131538171</v>
       </c>
       <c r="B10" t="n">
-        <v>57077</v>
+        <v>57078</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>131538191</v>
       </c>
       <c r="B11" t="n">
-        <v>57077</v>
+        <v>57078</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 9197-2026 artfynd.xlsx
+++ b/artfynd/A 9197-2026 artfynd.xlsx
@@ -1521,7 +1521,7 @@
         <v>131538171</v>
       </c>
       <c r="B10" t="n">
-        <v>57078</v>
+        <v>57081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>131538191</v>
       </c>
       <c r="B11" t="n">
-        <v>57078</v>
+        <v>57081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 9197-2026 artfynd.xlsx
+++ b/artfynd/A 9197-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1728,6 +1728,112 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131884101</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57081</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>dödad av predator</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skyltbäckrån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>567570</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6995130</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9197-2026 artfynd.xlsx
+++ b/artfynd/A 9197-2026 artfynd.xlsx
@@ -1521,7 +1521,7 @@
         <v>131538171</v>
       </c>
       <c r="B10" t="n">
-        <v>57081</v>
+        <v>57083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>131538191</v>
       </c>
       <c r="B11" t="n">
-        <v>57081</v>
+        <v>57083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>131884101</v>
       </c>
       <c r="B12" t="n">
-        <v>57081</v>
+        <v>57083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 9197-2026 artfynd.xlsx
+++ b/artfynd/A 9197-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1834,6 +1834,112 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131953391</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57084</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Råssåkerberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>567524</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6995219</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9197-2026 artfynd.xlsx
+++ b/artfynd/A 9197-2026 artfynd.xlsx
@@ -1521,7 +1521,7 @@
         <v>131538171</v>
       </c>
       <c r="B10" t="n">
-        <v>57083</v>
+        <v>57086</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>131538191</v>
       </c>
       <c r="B11" t="n">
-        <v>57083</v>
+        <v>57086</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>131884101</v>
       </c>
       <c r="B12" t="n">
-        <v>57083</v>
+        <v>57086</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>131953391</v>
       </c>
       <c r="B13" t="n">
-        <v>57084</v>
+        <v>57086</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 9197-2026 artfynd.xlsx
+++ b/artfynd/A 9197-2026 artfynd.xlsx
@@ -1521,7 +1521,7 @@
         <v>131538171</v>
       </c>
       <c r="B10" t="n">
-        <v>57086</v>
+        <v>57091</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>131538191</v>
       </c>
       <c r="B11" t="n">
-        <v>57086</v>
+        <v>57091</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>131884101</v>
       </c>
       <c r="B12" t="n">
-        <v>57086</v>
+        <v>57091</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>131953391</v>
       </c>
       <c r="B13" t="n">
-        <v>57086</v>
+        <v>57091</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
